--- a/src/test/output_test/Over_rate_regions/Region_over_200_400_1/Stats_over_200_400_1.xlsx
+++ b/src/test/output_test/Over_rate_regions/Region_over_200_400_1/Stats_over_200_400_1.xlsx
@@ -522,64 +522,64 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>119399</v>
+        <v>119405</v>
       </c>
       <c r="G2">
-        <v>341909.4228780135</v>
+        <v>358215</v>
       </c>
       <c r="H2">
-        <v>341.9094228780135</v>
+        <v>358.215</v>
       </c>
       <c r="I2">
-        <v>-1000</v>
+        <v>-997</v>
       </c>
       <c r="J2">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="K2">
-        <v>-47.28385497365974</v>
+        <v>-47.49585863238558</v>
       </c>
       <c r="L2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M2">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="N2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O2">
-        <v>231.5927521986361</v>
+        <v>230.5482371897567</v>
       </c>
       <c r="P2">
-        <v>-2.161208487535956</v>
+        <v>-2.165415020978165</v>
       </c>
       <c r="Q2">
-        <v>3.638664115165688</v>
+        <v>3.653326156916317</v>
       </c>
       <c r="R2">
-        <v>-436</v>
+        <v>-434</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V2">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
